--- a/db/ProyectoRedes_Claves.xlsx
+++ b/db/ProyectoRedes_Claves.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perci\Escritorio\8vo_Semestre\Redes\ProyectoFinal\ProyectoRedesFI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perci\Escritorio\8vo_Semestre\Redes\ProyectoFinal\ProyectoRedesFI\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C823C36-4038-44E7-9352-E8009E0EE7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFAB747-E537-4522-B3FF-8ACFCDE1991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23136" yWindow="-2400" windowWidth="11712" windowHeight="12336" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
+    <workbookView xWindow="-23148" yWindow="-2508" windowWidth="23256" windowHeight="12456" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>Contraseñas AP</t>
   </si>
@@ -135,6 +135,93 @@
   </si>
   <si>
     <t>PASSWORD SSH</t>
+  </si>
+  <si>
+    <t>PYTH0N#4</t>
+  </si>
+  <si>
+    <t>J4V4#8</t>
+  </si>
+  <si>
+    <t>USUARIO</t>
+  </si>
+  <si>
+    <t>P4RS3R#1</t>
+  </si>
+  <si>
+    <t>R3N3#7</t>
+  </si>
+  <si>
+    <t>F0UR1ER#4</t>
+  </si>
+  <si>
+    <t>L4PL4CE#9</t>
+  </si>
+  <si>
+    <t>V3VT0R$3</t>
+  </si>
+  <si>
+    <t>1NT3GRAL&amp;4</t>
+  </si>
+  <si>
+    <t>M1L1T4R#9</t>
+  </si>
+  <si>
+    <t>M1GU3L3$5</t>
+  </si>
+  <si>
+    <t>BL3ND3R#0</t>
+  </si>
+  <si>
+    <t>0P3NGL#777</t>
+  </si>
+  <si>
+    <t>R4Y0#8</t>
+  </si>
+  <si>
+    <t>L4$ER#5</t>
+  </si>
+  <si>
+    <t>L1NUX3R0</t>
+  </si>
+  <si>
+    <t>H1L0$#2</t>
+  </si>
+  <si>
+    <t>GP10#6</t>
+  </si>
+  <si>
+    <t>FPG4#4</t>
+  </si>
+  <si>
+    <t>10.0.0.7</t>
+  </si>
+  <si>
+    <t>DIRECCION IP</t>
+  </si>
+  <si>
+    <t>10.0.0.1</t>
+  </si>
+  <si>
+    <t>10.0.0.134</t>
+  </si>
+  <si>
+    <t>10.0.0.76</t>
+  </si>
+  <si>
+    <t>10.0.0.107</t>
+  </si>
+  <si>
+    <t>10.0.0.150</t>
+  </si>
+  <si>
+    <t>10.0.0.145</t>
+  </si>
+  <si>
+    <t>10.0.0.97</t>
+  </si>
+  <si>
+    <t>10.0.0.65</t>
   </si>
 </sst>
 </file>
@@ -166,7 +253,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -189,24 +276,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,8 +289,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,36 +626,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C17A4F0-2BEF-4586-A953-5709064D6E13}">
-  <dimension ref="B3:H17"/>
+  <dimension ref="B3:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -591,7 +672,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
@@ -602,7 +683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
@@ -613,7 +694,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
@@ -624,7 +705,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -635,119 +716,204 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="F11" s="1" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="H12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="H13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="J13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="L13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="F13" s="2" t="s">
+      <c r="E14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+      <c r="K14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="F14" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+      <c r="K15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="F15" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+      <c r="K16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="F16" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+      <c r="K17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="E18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="H12:L12"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="F11:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/ProyectoRedes_Claves.xlsx
+++ b/db/ProyectoRedes_Claves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perci\Escritorio\8vo_Semestre\Redes\ProyectoFinal\ProyectoRedesFI\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFAB747-E537-4522-B3FF-8ACFCDE1991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55344C2D-E176-407C-9434-15989513D127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-2508" windowWidth="23256" windowHeight="12456" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="209">
   <si>
     <t>Contraseñas AP</t>
   </si>
@@ -222,13 +222,457 @@
   </si>
   <si>
     <t>10.0.0.65</t>
+  </si>
+  <si>
+    <t>PLANTA PB</t>
+  </si>
+  <si>
+    <t>PLANTA_PB_DHCP</t>
+  </si>
+  <si>
+    <t>10.0.0.24</t>
+  </si>
+  <si>
+    <t>10.0.0.25</t>
+  </si>
+  <si>
+    <t>10.0.0.26</t>
+  </si>
+  <si>
+    <t>10.0.0.27</t>
+  </si>
+  <si>
+    <t>10.0.0.28</t>
+  </si>
+  <si>
+    <t>10.0.0.29</t>
+  </si>
+  <si>
+    <t>10.0.0.30</t>
+  </si>
+  <si>
+    <t>10.0.0.31</t>
+  </si>
+  <si>
+    <t>10.0.0.32</t>
+  </si>
+  <si>
+    <t>10.0.0.33</t>
+  </si>
+  <si>
+    <t>10.0.0.34</t>
+  </si>
+  <si>
+    <t>10.0.0.35</t>
+  </si>
+  <si>
+    <t>10.0.0.36</t>
+  </si>
+  <si>
+    <t>10.0.0.37</t>
+  </si>
+  <si>
+    <t>10.0.0.38</t>
+  </si>
+  <si>
+    <t>10.0.0.39</t>
+  </si>
+  <si>
+    <t>10.0.0.40</t>
+  </si>
+  <si>
+    <t>10.0.0.41</t>
+  </si>
+  <si>
+    <t>10.0.0.42</t>
+  </si>
+  <si>
+    <t>10.0.0.43</t>
+  </si>
+  <si>
+    <t>10.0.0.44</t>
+  </si>
+  <si>
+    <t>10.0.0.45</t>
+  </si>
+  <si>
+    <t>10.0.0.46</t>
+  </si>
+  <si>
+    <t>10.0.0.47</t>
+  </si>
+  <si>
+    <t>10.0.0.48</t>
+  </si>
+  <si>
+    <t>10.0.0.49</t>
+  </si>
+  <si>
+    <t>10.0.0.50</t>
+  </si>
+  <si>
+    <t>10.0.0.51</t>
+  </si>
+  <si>
+    <t>10.0.0.52</t>
+  </si>
+  <si>
+    <t>10.0.0.53</t>
+  </si>
+  <si>
+    <t>10.0.0.54</t>
+  </si>
+  <si>
+    <t>10.0.0.55</t>
+  </si>
+  <si>
+    <t>10.0.0.56</t>
+  </si>
+  <si>
+    <t>10.0.0.57</t>
+  </si>
+  <si>
+    <t>10.0.0.58</t>
+  </si>
+  <si>
+    <t>10.0.0.59</t>
+  </si>
+  <si>
+    <t>10.0.0.60</t>
+  </si>
+  <si>
+    <t>10.0.0.61</t>
+  </si>
+  <si>
+    <t>10.0.0.8</t>
+  </si>
+  <si>
+    <t>10.0.0.9</t>
+  </si>
+  <si>
+    <t>10.0.0.10</t>
+  </si>
+  <si>
+    <t>10.0.0.11</t>
+  </si>
+  <si>
+    <t>10.0.0.12</t>
+  </si>
+  <si>
+    <t>10.0.0.13</t>
+  </si>
+  <si>
+    <t>10.0.0.14</t>
+  </si>
+  <si>
+    <t>10.0.0.15</t>
+  </si>
+  <si>
+    <t>10.0.0.16</t>
+  </si>
+  <si>
+    <t>10.0.0.17</t>
+  </si>
+  <si>
+    <t>10.0.0.18</t>
+  </si>
+  <si>
+    <t>10.0.0.19</t>
+  </si>
+  <si>
+    <t>10.0.0.20</t>
+  </si>
+  <si>
+    <t>10.0.0.21</t>
+  </si>
+  <si>
+    <t>Servidores</t>
+  </si>
+  <si>
+    <t>Planta 1</t>
+  </si>
+  <si>
+    <t>Planta 2</t>
+  </si>
+  <si>
+    <t>Planta 3</t>
+  </si>
+  <si>
+    <t>Direcciones IPS Libres</t>
+  </si>
+  <si>
+    <t>10.0.0.135</t>
+  </si>
+  <si>
+    <t>10.0.0.136</t>
+  </si>
+  <si>
+    <t>10.0.0.137</t>
+  </si>
+  <si>
+    <t>10.0.0.138</t>
+  </si>
+  <si>
+    <t>10.0.0.139</t>
+  </si>
+  <si>
+    <t>10.0.0.140</t>
+  </si>
+  <si>
+    <t>10.0.0.141</t>
+  </si>
+  <si>
+    <t>10.0.0.142</t>
+  </si>
+  <si>
+    <t>10.0.0.77</t>
+  </si>
+  <si>
+    <t>10.0.0.95</t>
+  </si>
+  <si>
+    <t>10.0.0.78</t>
+  </si>
+  <si>
+    <t>10.0.0.79</t>
+  </si>
+  <si>
+    <t>10.0.0.80</t>
+  </si>
+  <si>
+    <t>10.0.0.81</t>
+  </si>
+  <si>
+    <t>10.0.0.82</t>
+  </si>
+  <si>
+    <t>10.0.0.83</t>
+  </si>
+  <si>
+    <t>10.0.0.84</t>
+  </si>
+  <si>
+    <t>10.0.0.85</t>
+  </si>
+  <si>
+    <t>10.0.0.86</t>
+  </si>
+  <si>
+    <t>10.0.0.87</t>
+  </si>
+  <si>
+    <t>10.0.0.88</t>
+  </si>
+  <si>
+    <t>10.0.0.89</t>
+  </si>
+  <si>
+    <t>10.0.0.90</t>
+  </si>
+  <si>
+    <t>10.0.0.91</t>
+  </si>
+  <si>
+    <t>10.0.0.92</t>
+  </si>
+  <si>
+    <t>10.0.0.93</t>
+  </si>
+  <si>
+    <t>10.0.0.94</t>
+  </si>
+  <si>
+    <t>10.0.0.108</t>
+  </si>
+  <si>
+    <t>10.0.0.109</t>
+  </si>
+  <si>
+    <t>10.0.0.110</t>
+  </si>
+  <si>
+    <t>10.0.0.111</t>
+  </si>
+  <si>
+    <t>10.0.0.112</t>
+  </si>
+  <si>
+    <t>10.0.0.113</t>
+  </si>
+  <si>
+    <t>10.0.0.114</t>
+  </si>
+  <si>
+    <t>10.0.0.115</t>
+  </si>
+  <si>
+    <t>10.0.0.116</t>
+  </si>
+  <si>
+    <t>10.0.0.117</t>
+  </si>
+  <si>
+    <t>10.0.0.118</t>
+  </si>
+  <si>
+    <t>10.0.0.119</t>
+  </si>
+  <si>
+    <t>10.0.0.120</t>
+  </si>
+  <si>
+    <t>10.0.0.121</t>
+  </si>
+  <si>
+    <t>10.0.0.122</t>
+  </si>
+  <si>
+    <t>10.0.0.123</t>
+  </si>
+  <si>
+    <t>10.0.0.124</t>
+  </si>
+  <si>
+    <t>10.0.0.125</t>
+  </si>
+  <si>
+    <t>10.0.0.126</t>
+  </si>
+  <si>
+    <t>10.0.0.151</t>
+  </si>
+  <si>
+    <t>10.0.0.152</t>
+  </si>
+  <si>
+    <t>10.0.0.153</t>
+  </si>
+  <si>
+    <t>10.0.0.154</t>
+  </si>
+  <si>
+    <t>10.0.0.155</t>
+  </si>
+  <si>
+    <t>10.0.0.156</t>
+  </si>
+  <si>
+    <t>10.0.0.157</t>
+  </si>
+  <si>
+    <t>10.0.0.158</t>
+  </si>
+  <si>
+    <t>10.0.0.159</t>
+  </si>
+  <si>
+    <t>Subred</t>
+  </si>
+  <si>
+    <t>Segmento de Red</t>
+  </si>
+  <si>
+    <t>Máscara de Red</t>
+  </si>
+  <si>
+    <t>Rango de IPs Útiles</t>
+  </si>
+  <si>
+    <t>Broadcast</t>
+  </si>
+  <si>
+    <t>Gateway</t>
+  </si>
+  <si>
+    <t>PB LAN</t>
+  </si>
+  <si>
+    <t>P1 LAN</t>
+  </si>
+  <si>
+    <t>P2 LAN</t>
+  </si>
+  <si>
+    <t>SERVIDORES</t>
+  </si>
+  <si>
+    <t>P3 LAN</t>
+  </si>
+  <si>
+    <t>PB-P1</t>
+  </si>
+  <si>
+    <t>PB-P2</t>
+  </si>
+  <si>
+    <t>PB-P3</t>
+  </si>
+  <si>
+    <t>10.0.0.0/26</t>
+  </si>
+  <si>
+    <t>10.0.0.64/27</t>
+  </si>
+  <si>
+    <t>10.0.0.96/27</t>
+  </si>
+  <si>
+    <t>10.0.0.128/28</t>
+  </si>
+  <si>
+    <t>10.0.0.144/28</t>
+  </si>
+  <si>
+    <t>10.0.0.160/30</t>
+  </si>
+  <si>
+    <t>10.0.0.164/30</t>
+  </si>
+  <si>
+    <t>10.0.0.168/30</t>
+  </si>
+  <si>
+    <t>255.255.255.192</t>
+  </si>
+  <si>
+    <t>255.255.255.224</t>
+  </si>
+  <si>
+    <t>255.255.255.240</t>
+  </si>
+  <si>
+    <t>255.255.255.252</t>
+  </si>
+  <si>
+    <t>10.0.0.127</t>
+  </si>
+  <si>
+    <t>10.0.0.143</t>
+  </si>
+  <si>
+    <t>10.0.0.163</t>
+  </si>
+  <si>
+    <t>10.0.0.167</t>
+  </si>
+  <si>
+    <t>10.0.0.171</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>10.0.0.129</t>
+  </si>
+  <si>
+    <t>10.0.0.63</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +684,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -280,16 +730,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -626,29 +1085,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C17A4F0-2BEF-4586-A953-5709064D6E13}">
-  <dimension ref="B3:L18"/>
+  <dimension ref="B3:N61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -717,20 +1176,20 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="H12" s="3" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="H12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
@@ -765,7 +1224,7 @@
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -780,7 +1239,7 @@
       <c r="F14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -797,7 +1256,7 @@
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -812,7 +1271,7 @@
       <c r="F15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>60</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -829,7 +1288,7 @@
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -844,7 +1303,7 @@
       <c r="F16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>59</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -860,8 +1319,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -876,7 +1335,7 @@
       <c r="F17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>58</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -892,8 +1351,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -909,12 +1368,612 @@
         <v>49</v>
       </c>
     </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="L23" s="5">
+        <v>62</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L24" s="5">
+        <v>30</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="L25" s="5">
+        <v>30</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L26" s="5">
+        <v>14</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="L27" s="5">
+        <v>14</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L28" s="5">
+        <v>2</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B29" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L29" s="5">
+        <v>2</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L30" s="5">
+        <v>2</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="5"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B32" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="5"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B36" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="5"/>
+      <c r="C37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B38" s="5"/>
+      <c r="C38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="5"/>
+      <c r="C39" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="5"/>
+      <c r="C40" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C43" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C44" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C45" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C46" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C47" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C48" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C54" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C59" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C60" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="H12:L12"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B21:G21"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/db/ProyectoRedes_Claves.xlsx
+++ b/db/ProyectoRedes_Claves.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perci\Escritorio\8vo_Semestre\Redes\ProyectoFinal\ProyectoRedesFI\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Angel Lara\Music\semestre8\RedesTeoria\Poryecto\db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55344C2D-E176-407C-9434-15989513D127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15D2CCB-EBF6-4330-834B-8C241076A06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{565147E7-335A-4F8E-A460-A735489A30ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="210">
   <si>
     <t>Contraseñas AP</t>
   </si>
@@ -666,6 +666,9 @@
   </si>
   <si>
     <t>10.0.0.63</t>
+  </si>
+  <si>
+    <t>10.0.0.149</t>
   </si>
 </sst>
 </file>
@@ -739,16 +742,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1086,30 +1089,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C17A4F0-2BEF-4586-A953-5709064D6E13}">
   <dimension ref="B3:N61"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
@@ -1142,7 +1145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1153,7 +1156,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1164,7 +1167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1175,23 +1178,23 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="H12" s="4" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="H12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>52</v>
       </c>
@@ -1223,7 +1226,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>51</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>54</v>
       </c>
@@ -1287,7 +1290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
@@ -1319,7 +1322,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>56</v>
       </c>
@@ -1351,7 +1354,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>57</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>119</v>
       </c>
@@ -1378,593 +1381,597 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B22" s="6" t="s">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" s="5" t="s">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="L23" s="4">
+        <v>62</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="L24" s="4">
+        <v>30</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="L23" s="5">
-        <v>62</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="I25" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="L25" s="4">
+        <v>30</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="L24" s="5">
-        <v>30</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N24" s="5" t="s">
+      <c r="I26" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L26" s="4">
+        <v>14</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L27" s="4">
+        <v>14</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L28" s="4">
+        <v>2</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L29" s="4">
+        <v>2</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="L30" s="4">
+        <v>2</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B25" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="L25" s="5">
-        <v>30</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B26" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L26" s="5">
-        <v>14</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B27" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L27" s="5">
-        <v>14</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B28" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="L28" s="5">
-        <v>2</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="N28" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B29" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="L29" s="5">
-        <v>2</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B30" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="L30" s="5">
-        <v>2</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="N30" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B31" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="5"/>
-      <c r="C37" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="5"/>
-      <c r="C38" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="5"/>
-      <c r="C39" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="5"/>
-      <c r="C40" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="5"/>
-      <c r="C41" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="5"/>
-      <c r="C42" s="5" t="s">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C43" s="5" t="s">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C44" s="5" t="s">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C45" s="5" t="s">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C46" s="5" t="s">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C47" s="5" t="s">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C47" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="C48" s="5" t="s">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C48" s="4" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C49" s="5" t="s">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C50" s="5" t="s">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C51" s="5" t="s">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C52" s="5" t="s">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C53" s="5" t="s">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C54" s="5" t="s">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C54" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C55" s="5" t="s">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C56" s="5" t="s">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C56" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C57" s="5" t="s">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C58" s="5" t="s">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C59" s="5" t="s">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C60" s="5" t="s">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C60" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C61" s="5"/>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
